--- a/Abilities.xlsx
+++ b/Abilities.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="88">
   <si>
     <t>Name</t>
   </si>
@@ -198,9 +198,6 @@
     <t>Slimey</t>
   </si>
   <si>
-    <t>After dying, deals 3 (Fire) damage to ALL units within 1 cell</t>
-  </si>
-  <si>
     <t>Putrid</t>
   </si>
   <si>
@@ -268,6 +265,21 @@
   </si>
   <si>
     <t>When deploying normally, can only be deployed in the further parts of the deployment zone</t>
+  </si>
+  <si>
+    <t>After dying, deals 2 (Fire) damage to ALL units within 1 cell</t>
+  </si>
+  <si>
+    <t>Woundable</t>
+  </si>
+  <si>
+    <t>If current half is half the maximu or lower, unit gains Weak</t>
+  </si>
+  <si>
+    <t>Unscoring</t>
+  </si>
+  <si>
+    <t>Cannot capture or contest objectives</t>
   </si>
 </sst>
 </file>
@@ -371,7 +383,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -388,13 +400,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -702,33 +717,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J58"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J62"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" style="3"/>
-    <col min="3" max="3" width="16.28515625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="72.85546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="3.85546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="3"/>
+    <col min="3" max="3" width="16.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="72.88671875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="3.88671875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="3" customWidth="1"/>
     <col min="7" max="7" width="45" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="44.85546875" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="3"/>
+    <col min="8" max="8" width="12.44140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="44.88671875" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -736,7 +751,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -756,10 +771,10 @@
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -783,8 +798,8 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>79</v>
+      <c r="A6" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>6</v>
@@ -805,22 +820,22 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C8" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" s="8" t="s">
+      <c r="F8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="2" t="s">
@@ -830,17 +845,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>8</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -850,17 +865,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="8" t="s">
+      <c r="F10" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="9" t="s">
         <v>26</v>
       </c>
       <c r="I10" s="2" t="s">
@@ -870,17 +885,17 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C12" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="F12" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I12" s="2" t="s">
@@ -890,17 +905,17 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="F13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>8</v>
       </c>
       <c r="I13" s="2" t="s">
@@ -910,17 +925,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="F14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>29</v>
       </c>
       <c r="I14" s="2" t="s">
@@ -930,7 +945,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C16" s="2" t="s">
         <v>0</v>
       </c>
@@ -950,7 +965,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C17" s="2" t="s">
         <v>5</v>
       </c>
@@ -990,7 +1005,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C20" s="2" t="s">
         <v>0</v>
       </c>
@@ -1010,7 +1025,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C21" s="2" t="s">
         <v>5</v>
       </c>
@@ -1030,7 +1045,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="3:10" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:10" ht="28.95" x14ac:dyDescent="0.3">
       <c r="C22" s="2" t="s">
         <v>6</v>
       </c>
@@ -1050,11 +1065,11 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C24" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D24" s="8" t="s">
+    <row r="24" spans="3:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="C24" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>24</v>
       </c>
       <c r="F24" s="4" t="s">
@@ -1063,18 +1078,18 @@
       <c r="G24" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I24" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="J24" s="8" t="s">
+      <c r="I24" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J24" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C25" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="8" t="s">
+    <row r="25" spans="3:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="C25" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F25" s="4" t="s">
@@ -1083,18 +1098,18 @@
       <c r="G25" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I25" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="J25" s="8" t="s">
+      <c r="I25" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J25" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="26" spans="3:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="8" t="s">
+      <c r="C26" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>27</v>
       </c>
       <c r="F26" s="4" t="s">
@@ -1103,85 +1118,85 @@
       <c r="G26" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="I26" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C28" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="4" t="s">
+      <c r="I26" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="F28" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="I28" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C29" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="4" t="s">
+      <c r="I28" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="4" t="s">
+      <c r="F29" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="J29" s="8" t="s">
+      <c r="I29" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="3:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="C30" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="4" t="s">
+    <row r="30" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G30" s="4" t="s">
+      <c r="F30" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G30" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="I30" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="J30" s="8" t="s">
+      <c r="I30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J30" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C32" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>78</v>
+      <c r="F32" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>77</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>0</v>
@@ -1197,10 +1212,10 @@
       <c r="D33" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="4" t="s">
+      <c r="F33" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>8</v>
       </c>
       <c r="I33" s="4" t="s">
@@ -1210,18 +1225,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="3:10" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C34" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>60</v>
+      <c r="F34" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>83</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>6</v>
@@ -1230,7 +1245,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C36" s="4" t="s">
         <v>0</v>
       </c>
@@ -1241,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>0</v>
@@ -1250,7 +1265,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C37" s="4" t="s">
         <v>5</v>
       </c>
@@ -1270,7 +1285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="3:10" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C38" s="4" t="s">
         <v>6</v>
       </c>
@@ -1281,40 +1296,40 @@
         <v>6</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="40" spans="3:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C40" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F40"/>
-      <c r="G40"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
       <c r="I40" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="41" spans="3:10" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C41" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F41"/>
-      <c r="G41"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
       <c r="I41" s="4" t="s">
         <v>5</v>
       </c>
@@ -1322,23 +1337,23 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C42" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F42"/>
-      <c r="G42"/>
+        <v>66</v>
+      </c>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
       <c r="I42" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="44" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C44" s="4" t="s">
         <v>0</v>
       </c>
@@ -1349,10 +1364,10 @@
         <v>0</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="45" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C45" s="4" t="s">
         <v>5</v>
       </c>
@@ -1366,7 +1381,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="3:10" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C46" s="4" t="s">
         <v>6</v>
       </c>
@@ -1377,24 +1392,24 @@
         <v>6</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="48" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C48" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="49" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C49" s="4" t="s">
         <v>5</v>
       </c>
@@ -1408,35 +1423,35 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C50" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="52" spans="3:10" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="52" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C52" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="53" spans="3:10" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C53" s="4" t="s">
         <v>5</v>
       </c>
@@ -1450,42 +1465,84 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="3:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C54" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="56" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C56" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="57" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="57" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C57" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="3:10" ht="55.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I57" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="3:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C58" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="60" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I60" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="61" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I61" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1499,9 +1556,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1511,7 +1568,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Abilities.xlsx
+++ b/Abilities.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="148">
   <si>
     <t>Name</t>
   </si>
@@ -147,9 +147,6 @@
     <t>Conductive</t>
   </si>
   <si>
-    <t>All lightning damage within 1 cell is redirected into this unit</t>
-  </si>
-  <si>
     <t>Each time this unit is dealt damage by an attacker, attacker receives 1 Damage of the same type</t>
   </si>
   <si>
@@ -280,13 +277,196 @@
   </si>
   <si>
     <t>Cannot capture or contest objectives</t>
+  </si>
+  <si>
+    <t>All lightning damage within 1 cell is redirected into this unit. Gains 1 attack damage for each Lightning damage received</t>
+  </si>
+  <si>
+    <t>Randomized</t>
+  </si>
+  <si>
+    <t>When deployed, maximum Health, Attack damage amount and type are set randomly</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>Between 1-6</t>
+  </si>
+  <si>
+    <t>Damage type</t>
+  </si>
+  <si>
+    <t>Physical, Fire, Lightning or Frost</t>
+  </si>
+  <si>
+    <t>Damage amount</t>
+  </si>
+  <si>
+    <t>Between 1-2</t>
+  </si>
+  <si>
+    <t>Scavenging</t>
+  </si>
+  <si>
+    <t>Each time a unit within 1 cell of this unit dies, player receives 1 Item</t>
+  </si>
+  <si>
+    <t>Strengthened</t>
+  </si>
+  <si>
+    <t>Next attack deals 1 extra Damage</t>
+  </si>
+  <si>
+    <t>Polymorphed</t>
+  </si>
+  <si>
+    <t>The unit uses stats of "Polymorphed animal" except for the Size, which remains the same. Expires at the end of opponent's turn or when polymorphed unit reaches 0 health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydrokinesis </t>
+  </si>
+  <si>
+    <t>When moving, all "Water" covers within 3 cells move in the same relative direction</t>
+  </si>
+  <si>
+    <t>Oliokinesis</t>
+  </si>
+  <si>
+    <t>When moving, all "Oil" covers within 3 cells move in the same relative direction</t>
+  </si>
+  <si>
+    <t>Stormokinesis</t>
+  </si>
+  <si>
+    <t>After attacking a cell, covers it in "Storm cloud"</t>
+  </si>
+  <si>
+    <t>Charging</t>
+  </si>
+  <si>
+    <t>Freezing</t>
+  </si>
+  <si>
+    <t>Applies "Vulnerable:Frost" to all units within 2 cells</t>
+  </si>
+  <si>
+    <t>Can move through other units, but doing so deals unit's attack damage to that unit</t>
+  </si>
+  <si>
+    <t>Merging</t>
+  </si>
+  <si>
+    <t>After passing your turn, Merges with all units within 1 cell with this ability</t>
+  </si>
+  <si>
+    <t>Name: Base titles randomly arranged, then abilities additions</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Slippery ""</t>
+  </si>
+  <si>
+    <t>"" oozing with oil</t>
+  </si>
+  <si>
+    <t>Blind ""</t>
+  </si>
+  <si>
+    <t>"" dripping with water</t>
+  </si>
+  <si>
+    <t>"" what is actually 3 goblins</t>
+  </si>
+  <si>
+    <t>"" slimey with toxin</t>
+  </si>
+  <si>
+    <t>cowardly ""</t>
+  </si>
+  <si>
+    <t>penetrating ""</t>
+  </si>
+  <si>
+    <t>Cursed ""</t>
+  </si>
+  <si>
+    <t>mad ""</t>
+  </si>
+  <si>
+    <t>Putrid ""</t>
+  </si>
+  <si>
+    <t>Weak ""</t>
+  </si>
+  <si>
+    <t>"" the lord of beasts</t>
+  </si>
+  <si>
+    <t>bloodthirsty ""</t>
+  </si>
+  <si>
+    <t>Decaying ""</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title </t>
+  </si>
+  <si>
+    <t>Polymorphed ""</t>
+  </si>
+  <si>
+    <t>vampiric ""</t>
+  </si>
+  <si>
+    <t>hydrokinetic ""</t>
+  </si>
+  <si>
+    <t>oilokinetic ""</t>
+  </si>
+  <si>
+    <t>Scavenging ""</t>
+  </si>
+  <si>
+    <t>stormokinetic ""</t>
+  </si>
+  <si>
+    <t>Charging ""</t>
+  </si>
+  <si>
+    <t>Size: Combined, up to 4x or random biggest one of the merged units if its higher</t>
+  </si>
+  <si>
+    <t>Max, current health, Damage, Keywords: Sum of all merged units</t>
+  </si>
+  <si>
+    <t>Damage type, Movement, Attacks: Random out of merged</t>
+  </si>
+  <si>
+    <t>Pushing</t>
+  </si>
+  <si>
+    <t>All units damaged by attacks are pushed away from the unit</t>
+  </si>
+  <si>
+    <t>Sucking</t>
+  </si>
+  <si>
+    <t>sucking ""</t>
+  </si>
+  <si>
+    <t>All units damaged by attacks are pulled towards the unit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,6 +499,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -383,7 +571,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -406,11 +594,21 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -717,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" style="3" customWidth="1"/>
@@ -734,14 +932,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
@@ -771,600 +973,659 @@
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="1" t="s">
+      <c r="I6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="1" t="s">
+    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="F7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J6" s="1" t="s">
+      <c r="I7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C9" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="9" t="s">
+      <c r="F11" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="I11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="9" t="s">
+    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J10" s="2" t="s">
+      <c r="I12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C14" s="2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C16" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>59</v>
+        <v>12</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>8</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C17" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C20" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="F24" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="s">
+      <c r="I24" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="2" t="s">
+    <row r="25" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="F26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="4" t="s">
+      <c r="I26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="3:10" ht="28.95" x14ac:dyDescent="0.3">
-      <c r="C22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="2" t="s">
+    <row r="27" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J22" s="4" t="s">
+      <c r="F27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J27" s="4" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="C24" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="C25" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="29" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C29" s="7" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D29" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C30" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F29" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="9" t="s">
+      <c r="F31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J29" s="7" t="s">
+      <c r="I31" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J31" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C30" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="J30" s="7" t="s">
+    <row r="32" spans="3:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C34" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C36" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C37" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J37" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D32" s="4" t="s">
+    <row r="39" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C39" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F32" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J32" s="4" t="s">
+      <c r="F39" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="3:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J41" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="3:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="4" t="s">
+    <row r="43" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C43" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F34" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C36" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J36" s="4" t="s">
+      <c r="F43" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C37" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C38" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C40" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="I40" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C41" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="I41" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C42" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="I42" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="44" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C44" s="4" t="s">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>55</v>
+        <v>116</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>127</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" spans="3:10" x14ac:dyDescent="0.3">
@@ -1374,6 +1635,12 @@
       <c r="D45" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="F45" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="I45" s="4" t="s">
         <v>5</v>
       </c>
@@ -1386,13 +1653,19 @@
         <v>6</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="3:10" x14ac:dyDescent="0.3">
@@ -1400,156 +1673,700 @@
         <v>0</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>62</v>
+        <v>51</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="49" spans="3:10" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C49" s="4" t="s">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>12</v>
+        <v>129</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C50" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D50" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="I50" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>76</v>
+      <c r="F51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C52" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>81</v>
+      <c r="F52" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="53" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C53" s="4" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D53" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C54" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="55" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C55" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I53" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J53" s="4" t="s">
+      <c r="I55" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J55" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C54" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C56" s="4" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D56" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C58" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59" spans="3:10" s="10" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C59" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C60" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="3:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C63" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C64" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="65" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C65" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="68" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C68" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C69" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="70" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C70" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="3:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="I56" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J56" s="4" t="s">
+      <c r="F71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J71" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C57" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D57" s="4" t="s">
+    <row r="73" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C73" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="74" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C74" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="75" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C75" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I57" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J57" s="4" t="s">
+      <c r="F75" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J75" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="3:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C58" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="I58" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="60" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="I60" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J60" s="4" t="s">
+    <row r="76" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J76" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="61" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="I61" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="62" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="I62" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>87</v>
+    <row r="78" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C78" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="79" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C79" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="80" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C80" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C81" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="83" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C83" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="84" spans="3:7" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C84" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="85" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C85" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C86" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="87" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F87" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="88" spans="3:7" ht="24" x14ac:dyDescent="0.3">
+      <c r="F88" s="13"/>
+      <c r="G88" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="89" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F89" s="13"/>
+      <c r="G89" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="90" spans="3:7" ht="24" x14ac:dyDescent="0.3">
+      <c r="F90" s="13"/>
+      <c r="G90" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="91" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F91" s="12"/>
+      <c r="G91"/>
+    </row>
+    <row r="92" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F92" s="12"/>
+      <c r="G92"/>
+    </row>
+    <row r="93" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F93" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="94" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F94" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="95" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F95" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F96" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="97" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C97"/>
+      <c r="D97"/>
+    </row>
+    <row r="98" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C98"/>
+      <c r="D98"/>
+      <c r="F98" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="99" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F99" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="100" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F100" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F101" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="F87:F90"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Abilities.xlsx
+++ b/Abilities.xlsx
@@ -264,9 +264,6 @@
     <t>When deploying normally, can only be deployed in the further parts of the deployment zone</t>
   </si>
   <si>
-    <t>After dying, deals 2 (Fire) damage to ALL units within 1 cell</t>
-  </si>
-  <si>
     <t>Woundable</t>
   </si>
   <si>
@@ -460,6 +457,9 @@
   </si>
   <si>
     <t>All units damaged by attacks are pulled towards the unit</t>
+  </si>
+  <si>
+    <t>After dying, deals 1 (Fire) damage to ALL units within 1 cell</t>
   </si>
 </sst>
 </file>
@@ -603,10 +603,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -932,18 +932,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
@@ -979,22 +979,22 @@
     <row r="5" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="C5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="I5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -1070,22 +1070,22 @@
     </row>
     <row r="10" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="F10" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G10" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1150,22 +1150,22 @@
     </row>
     <row r="15" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="F15" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1250,22 +1250,22 @@
     </row>
     <row r="21" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C21" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="I21" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="22" spans="3:10" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1310,22 +1310,22 @@
     </row>
     <row r="25" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C25" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>42</v>
       </c>
       <c r="I25" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J25" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="26" spans="3:10" x14ac:dyDescent="0.3">
@@ -1359,7 +1359,7 @@
         <v>6</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>6</v>
@@ -1390,22 +1390,22 @@
     </row>
     <row r="30" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C30" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>116</v>
-      </c>
       <c r="F30" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G30" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="J30" s="7" t="s">
         <v>125</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="31" spans="3:10" x14ac:dyDescent="0.3">
@@ -1470,22 +1470,22 @@
     </row>
     <row r="35" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C35" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>116</v>
-      </c>
       <c r="F35" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G35" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="G35" s="8" t="s">
-        <v>116</v>
-      </c>
       <c r="I35" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="J35" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="36" spans="3:10" x14ac:dyDescent="0.3">
@@ -1578,8 +1578,8 @@
       <c r="F41" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G41" s="8" t="s">
-        <v>82</v>
+      <c r="G41" s="7" t="s">
+        <v>147</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>6</v>
@@ -1610,22 +1610,22 @@
     </row>
     <row r="44" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C44" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>116</v>
-      </c>
       <c r="F44" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G44" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J44" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="45" spans="3:10" x14ac:dyDescent="0.3">
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>0</v>
@@ -1690,22 +1690,22 @@
     </row>
     <row r="49" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C49" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G49" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="I49" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J49" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="50" spans="3:10" x14ac:dyDescent="0.3">
@@ -1739,7 +1739,7 @@
         <v>6</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>6</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="52" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F52" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="G52" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="53" spans="3:10" x14ac:dyDescent="0.3">
@@ -1764,10 +1764,10 @@
         <v>54</v>
       </c>
       <c r="F53" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="G53" s="9" t="s">
         <v>92</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>93</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>0</v>
@@ -1778,22 +1778,22 @@
     </row>
     <row r="54" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C54" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>116</v>
-      </c>
       <c r="F54" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G54" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="G54" s="9" t="s">
-        <v>95</v>
-      </c>
       <c r="I54" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="3:10" x14ac:dyDescent="0.3">
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>0</v>
@@ -1846,22 +1846,22 @@
     </row>
     <row r="59" spans="3:10" s="10" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C59" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G59" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="I59" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" spans="3:10" x14ac:dyDescent="0.3">
@@ -1895,7 +1895,7 @@
         <v>6</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>6</v>
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>0</v>
@@ -1926,22 +1926,22 @@
     </row>
     <row r="64" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C64" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D64" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G64" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>135</v>
-      </c>
       <c r="I64" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="65" spans="3:10" x14ac:dyDescent="0.3">
@@ -1975,7 +1975,7 @@
         <v>6</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>6</v>
@@ -1995,33 +1995,33 @@
         <v>0</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C69" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="70" spans="3:10" x14ac:dyDescent="0.3">
@@ -2055,13 +2055,13 @@
         <v>6</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="73" spans="3:10" x14ac:dyDescent="0.3">
@@ -2069,39 +2069,39 @@
         <v>0</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="74" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C74" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D74" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G74" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F74" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="I74" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="75" spans="3:10" x14ac:dyDescent="0.3">
@@ -2129,19 +2129,19 @@
         <v>6</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78" spans="3:10" x14ac:dyDescent="0.3">
@@ -2149,27 +2149,27 @@
         <v>0</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C79" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80" spans="3:10" x14ac:dyDescent="0.3">
@@ -2191,13 +2191,13 @@
         <v>6</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="83" spans="3:7" x14ac:dyDescent="0.3">
@@ -2205,27 +2205,27 @@
         <v>0</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="84" spans="3:7" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C84" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="85" spans="3:7" x14ac:dyDescent="0.3">
@@ -2247,47 +2247,47 @@
         <v>6</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="87" spans="3:7" x14ac:dyDescent="0.3">
       <c r="F87" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88" spans="3:7" ht="24" x14ac:dyDescent="0.3">
       <c r="F88" s="13"/>
       <c r="G88" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="89" spans="3:7" x14ac:dyDescent="0.3">
       <c r="F89" s="13"/>
       <c r="G89" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="90" spans="3:7" ht="24" x14ac:dyDescent="0.3">
       <c r="F90" s="13"/>
       <c r="G90" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="91" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="F91" s="12"/>
+      <c r="F91" s="11"/>
       <c r="G91"/>
     </row>
     <row r="92" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="F92" s="12"/>
+      <c r="F92" s="11"/>
       <c r="G92"/>
     </row>
     <row r="93" spans="3:7" x14ac:dyDescent="0.3">
@@ -2295,15 +2295,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="94" spans="3:7" x14ac:dyDescent="0.3">
       <c r="F94" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="95" spans="3:7" x14ac:dyDescent="0.3">
@@ -2319,7 +2319,7 @@
         <v>6</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="97" spans="3:7" x14ac:dyDescent="0.3">
@@ -2333,15 +2333,15 @@
         <v>0</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="99" spans="3:7" x14ac:dyDescent="0.3">
       <c r="F99" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="100" spans="3:7" x14ac:dyDescent="0.3">
@@ -2357,7 +2357,7 @@
         <v>6</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/Abilities.xlsx
+++ b/Abilities.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="153">
   <si>
     <t>Name</t>
   </si>
@@ -78,12 +78,6 @@
     <t>Cowardly</t>
   </si>
   <si>
-    <t>Beckoned</t>
-  </si>
-  <si>
-    <t>Can only move towards the enemy deployment zone</t>
-  </si>
-  <si>
     <t>Cannot be moved within 1 cell of enemy units</t>
   </si>
   <si>
@@ -237,9 +231,6 @@
     <t>A game of skeletons</t>
   </si>
   <si>
-    <t>At the start of your turn, creates a 'Skelic' unit is created. If a unit created this way has 2 or more 'Skelic' units within 1 cell, it is immedeatly destroyed</t>
-  </si>
-  <si>
     <t>Temporary (1,2)</t>
   </si>
   <si>
@@ -306,9 +297,6 @@
     <t>Scavenging</t>
   </si>
   <si>
-    <t>Each time a unit within 1 cell of this unit dies, player receives 1 Item</t>
-  </si>
-  <si>
     <t>Strengthened</t>
   </si>
   <si>
@@ -333,9 +321,6 @@
     <t>When moving, all "Oil" covers within 3 cells move in the same relative direction</t>
   </si>
   <si>
-    <t>Stormokinesis</t>
-  </si>
-  <si>
     <t>After attacking a cell, covers it in "Storm cloud"</t>
   </si>
   <si>
@@ -354,12 +339,6 @@
     <t>Merging</t>
   </si>
   <si>
-    <t>After passing your turn, Merges with all units within 1 cell with this ability</t>
-  </si>
-  <si>
-    <t>Name: Base titles randomly arranged, then abilities additions</t>
-  </si>
-  <si>
     <t>Title</t>
   </si>
   <si>
@@ -429,9 +408,6 @@
     <t>Scavenging ""</t>
   </si>
   <si>
-    <t>stormokinetic ""</t>
-  </si>
-  <si>
     <t>Charging ""</t>
   </si>
   <si>
@@ -441,9 +417,6 @@
     <t>Max, current health, Damage, Keywords: Sum of all merged units</t>
   </si>
   <si>
-    <t>Damage type, Movement, Attacks: Random out of merged</t>
-  </si>
-  <si>
     <t>Pushing</t>
   </si>
   <si>
@@ -460,6 +433,48 @@
   </si>
   <si>
     <t>After dying, deals 1 (Fire) damage to ALL units within 1 cell</t>
+  </si>
+  <si>
+    <t>Beckoned (X)</t>
+  </si>
+  <si>
+    <t>Selects a random enemy unit. Can only be moved towards that unit</t>
+  </si>
+  <si>
+    <t>Captivating</t>
+  </si>
+  <si>
+    <t>captivating ""</t>
+  </si>
+  <si>
+    <t>While an enemy unit is within 3 squares, receives "Beckoned" towards this unit</t>
+  </si>
+  <si>
+    <t>Damage type, Movement, Attacks: Random out of merged (If max range is same, one with more total cells is prioritised)</t>
+  </si>
+  <si>
+    <t>Name: Base names alphabetically arranged, then abilities additions</t>
+  </si>
+  <si>
+    <t>At the start of the round, creates a 'Skelic' unit nearby. Afterwards, if if this unit is standing next to 2 or more units with this Ability, it is immedeatly destroyed</t>
+  </si>
+  <si>
+    <t>At the start of the round, Merges with all units within 1 cell with this ability</t>
+  </si>
+  <si>
+    <t>Each time a unit nearby dies, player receives 1 Item</t>
+  </si>
+  <si>
+    <t>Stormbender</t>
+  </si>
+  <si>
+    <t>"" bender of storms</t>
+  </si>
+  <si>
+    <t>Enfeebled</t>
+  </si>
+  <si>
+    <t>Next attack deals 1 less Damage</t>
   </si>
 </sst>
 </file>
@@ -915,7 +930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" style="3" customWidth="1"/>
@@ -961,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>0</v>
@@ -973,28 +988,28 @@
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -1022,13 +1037,13 @@
     </row>
     <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>6</v>
@@ -1040,7 +1055,7 @@
         <v>6</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1053,13 +1068,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>0</v>
@@ -1070,22 +1085,22 @@
     </row>
     <row r="10" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1113,13 +1128,13 @@
         <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>6</v>
@@ -1139,33 +1154,33 @@
         <v>0</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C15" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1181,14 +1196,14 @@
       <c r="G16" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J16" s="2" t="s">
+      <c r="I16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J16" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C17" s="2" t="s">
         <v>6</v>
       </c>
@@ -1199,13 +1214,13 @@
         <v>6</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.3">
@@ -1219,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>0</v>
@@ -1250,22 +1265,22 @@
     </row>
     <row r="21" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C21" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>121</v>
-      </c>
       <c r="I21" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="3:10" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1279,13 +1294,13 @@
         <v>6</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.3">
@@ -1293,39 +1308,39 @@
         <v>0</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C25" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="3:10" x14ac:dyDescent="0.3">
@@ -1353,19 +1368,19 @@
         <v>6</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="3:10" x14ac:dyDescent="0.3">
@@ -1373,39 +1388,39 @@
         <v>0</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>0</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C30" s="7" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="3:10" x14ac:dyDescent="0.3">
@@ -1433,19 +1448,19 @@
         <v>6</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>6</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.3">
@@ -1453,39 +1468,39 @@
         <v>0</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>0</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C35" s="7" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="3:10" x14ac:dyDescent="0.3">
@@ -1513,19 +1528,19 @@
         <v>6</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>6</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.3">
@@ -1533,19 +1548,19 @@
         <v>0</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1573,19 +1588,19 @@
         <v>6</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="3:10" x14ac:dyDescent="0.3">
@@ -1593,39 +1608,39 @@
         <v>0</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C44" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="3:10" x14ac:dyDescent="0.3">
@@ -1653,19 +1668,19 @@
         <v>6</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48" spans="3:10" x14ac:dyDescent="0.3">
@@ -1673,39 +1688,39 @@
         <v>0</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C49" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="3:10" x14ac:dyDescent="0.3">
@@ -1733,27 +1748,27 @@
         <v>6</v>
       </c>
       <c r="D51" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J51" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="52" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F52" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="3:10" x14ac:dyDescent="0.3">
@@ -1761,39 +1776,39 @@
         <v>0</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C54" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="3:10" x14ac:dyDescent="0.3">
@@ -1815,13 +1830,13 @@
         <v>6</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="3:10" x14ac:dyDescent="0.3">
@@ -1829,39 +1844,39 @@
         <v>0</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="3:10" s="10" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C59" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="3:10" x14ac:dyDescent="0.3">
@@ -1889,19 +1904,19 @@
         <v>6</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="3:10" x14ac:dyDescent="0.3">
@@ -1909,39 +1924,39 @@
         <v>0</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C64" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65" spans="3:10" x14ac:dyDescent="0.3">
@@ -1969,19 +1984,19 @@
         <v>6</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68" spans="3:10" x14ac:dyDescent="0.3">
@@ -1989,39 +2004,39 @@
         <v>0</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C69" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70" spans="3:10" x14ac:dyDescent="0.3">
@@ -2049,19 +2064,19 @@
         <v>6</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73" spans="3:10" x14ac:dyDescent="0.3">
@@ -2069,39 +2084,39 @@
         <v>0</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C74" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="3:10" x14ac:dyDescent="0.3">
@@ -2129,19 +2144,19 @@
         <v>6</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="78" spans="3:10" x14ac:dyDescent="0.3">
@@ -2149,27 +2164,39 @@
         <v>0</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="79" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C79" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="80" spans="3:10" x14ac:dyDescent="0.3">
@@ -2185,50 +2212,62 @@
       <c r="G80" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="81" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="I80" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C81" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="83" spans="3:7" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="83" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C83" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="84" spans="3:7" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="84" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C84" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="85" spans="3:7" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="85" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C85" s="4" t="s">
         <v>5</v>
       </c>
@@ -2242,71 +2281,71 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C86" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="87" spans="3:7" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="87" spans="3:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F87" s="13" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="88" spans="3:7" ht="24" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="88" spans="3:10" ht="24" x14ac:dyDescent="0.3">
       <c r="F88" s="13"/>
       <c r="G88" s="9" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="89" spans="3:7" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="89" spans="3:10" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F89" s="13"/>
       <c r="G89" s="9" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="90" spans="3:7" ht="24" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="90" spans="3:10" ht="24" x14ac:dyDescent="0.3">
       <c r="F90" s="13"/>
       <c r="G90" s="9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="91" spans="3:7" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="91" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F91" s="11"/>
       <c r="G91"/>
     </row>
-    <row r="92" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F92" s="11"/>
       <c r="G92"/>
     </row>
-    <row r="93" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F93" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="94" spans="3:7" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="94" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F94" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="95" spans="3:7" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="95" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2314,12 +2353,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="F96" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
     </row>
     <row r="97" spans="3:7" x14ac:dyDescent="0.3">
@@ -2333,15 +2372,15 @@
         <v>0</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
     </row>
     <row r="99" spans="3:7" x14ac:dyDescent="0.3">
       <c r="F99" s="4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="100" spans="3:7" x14ac:dyDescent="0.3">
@@ -2357,7 +2396,39 @@
         <v>6</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>146</v>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="103" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F103" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="104" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F104" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="105" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F105" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F106" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/Abilities.xlsx
+++ b/Abilities.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="161">
   <si>
     <t>Name</t>
   </si>
@@ -177,9 +177,6 @@
     <t>Teleportation beacon</t>
   </si>
   <si>
-    <t>Can deploy other units on this unit's position, but doing so takes 1 extra turn and destroyes this unit</t>
-  </si>
-  <si>
     <t>Immovable</t>
   </si>
   <si>
@@ -192,9 +189,6 @@
     <t>Putrid</t>
   </si>
   <si>
-    <t>After dying, deals 3 (Poison) damage to ALL units within 1 cell</t>
-  </si>
-  <si>
     <t>Weakening</t>
   </si>
   <si>
@@ -219,9 +213,6 @@
     <t>Vampiric</t>
   </si>
   <si>
-    <t>After a unit within 1 cell is destroyed, this unit's attacks gain 1 damage</t>
-  </si>
-  <si>
     <t>Decaying</t>
   </si>
   <si>
@@ -306,9 +297,6 @@
     <t>Polymorphed</t>
   </si>
   <si>
-    <t>The unit uses stats of "Polymorphed animal" except for the Size, which remains the same. Expires at the end of opponent's turn or when polymorphed unit reaches 0 health</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hydrokinesis </t>
   </si>
   <si>
@@ -462,9 +450,6 @@
     <t>At the start of the round, Merges with all units within 1 cell with this ability</t>
   </si>
   <si>
-    <t>Each time a unit nearby dies, player receives 1 Item</t>
-  </si>
-  <si>
     <t>Stormbender</t>
   </si>
   <si>
@@ -475,6 +460,45 @@
   </si>
   <si>
     <t>Next attack deals 1 less Damage</t>
+  </si>
+  <si>
+    <t>Each time a unit within 1 cell is destroyed, this unit gains 1 attack damage</t>
+  </si>
+  <si>
+    <t>Can deploy other units on this unit's position, but doing so takes 1 extra turn and destroys this unit</t>
+  </si>
+  <si>
+    <t>After dying, deals 1 (Poison) damage to ALL units within 1 cell</t>
+  </si>
+  <si>
+    <t>The unit uses stats of "Polymorphed animal" but remains the same size. Expires at the end of opponent's turn or when polymorphed unit reaches 0 health</t>
+  </si>
+  <si>
+    <t>Bladeguarded</t>
+  </si>
+  <si>
+    <t>"" guarded by spinning blades</t>
+  </si>
+  <si>
+    <t>Deals 1 (Physical) damage to all enemies within a 2 cell square ring</t>
+  </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
+    <t>Functions as temporary additional maximum health, but is only restored when additional "Extra health (X)" ability is applied</t>
+  </si>
+  <si>
+    <t>Extra healthy (X)</t>
+  </si>
+  <si>
+    <t>Safeguarded</t>
+  </si>
+  <si>
+    <t>First instance of incoming damage deals 0 damage. Ability is consumed afterwards</t>
+  </si>
+  <si>
+    <t>The first time player uses an item when this unit is on the battlefield, another item is immedeatly drawn</t>
   </si>
 </sst>
 </file>
@@ -555,7 +579,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -578,6 +602,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -586,7 +647,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -622,7 +683,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -947,18 +1017,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
@@ -988,28 +1058,28 @@
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -1037,7 +1107,7 @@
     </row>
     <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
@@ -1085,22 +1155,22 @@
     </row>
     <row r="10" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1160,27 +1230,27 @@
         <v>0</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C15" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>112</v>
-      </c>
       <c r="I15" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1220,7 +1290,7 @@
         <v>6</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.3">
@@ -1234,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>0</v>
@@ -1265,22 +1335,22 @@
     </row>
     <row r="21" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C21" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="3:10" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1325,22 +1395,22 @@
     </row>
     <row r="25" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C25" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>40</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="3:10" x14ac:dyDescent="0.3">
@@ -1374,7 +1444,7 @@
         <v>6</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>6</v>
@@ -1405,22 +1475,22 @@
     </row>
     <row r="30" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C30" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="3:10" x14ac:dyDescent="0.3">
@@ -1460,7 +1530,7 @@
         <v>6</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.3">
@@ -1474,33 +1544,33 @@
         <v>0</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>0</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C35" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="3:10" x14ac:dyDescent="0.3">
@@ -1534,7 +1604,7 @@
         <v>6</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>6</v>
@@ -1554,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>0</v>
@@ -1594,7 +1664,7 @@
         <v>6</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>6</v>
@@ -1614,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>0</v>
@@ -1625,22 +1695,22 @@
     </row>
     <row r="44" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C44" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="3:10" x14ac:dyDescent="0.3">
@@ -1674,13 +1744,13 @@
         <v>6</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="3:10" x14ac:dyDescent="0.3">
@@ -1694,33 +1764,33 @@
         <v>0</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C49" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="3:10" x14ac:dyDescent="0.3">
@@ -1748,27 +1818,27 @@
         <v>6</v>
       </c>
       <c r="D51" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J51" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="52" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F52" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="3:10" x14ac:dyDescent="0.3">
@@ -1779,36 +1849,36 @@
         <v>52</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C54" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="3:10" x14ac:dyDescent="0.3">
@@ -1830,13 +1900,13 @@
         <v>6</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58" spans="3:10" x14ac:dyDescent="0.3">
@@ -1844,39 +1914,39 @@
         <v>0</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="3:10" s="10" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C59" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60" spans="3:10" x14ac:dyDescent="0.3">
@@ -1904,19 +1974,19 @@
         <v>6</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>96</v>
+        <v>151</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="3:10" x14ac:dyDescent="0.3">
@@ -1924,39 +1994,39 @@
         <v>0</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="64" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C64" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="3:10" x14ac:dyDescent="0.3">
@@ -1984,19 +2054,19 @@
         <v>6</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>67</v>
+        <v>148</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="3:10" x14ac:dyDescent="0.3">
@@ -2004,39 +2074,39 @@
         <v>0</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C69" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G69" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>128</v>
-      </c>
       <c r="I69" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="70" spans="3:10" x14ac:dyDescent="0.3">
@@ -2064,19 +2134,19 @@
         <v>6</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="3:10" x14ac:dyDescent="0.3">
@@ -2084,39 +2154,39 @@
         <v>0</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C74" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="75" spans="3:10" x14ac:dyDescent="0.3">
@@ -2139,24 +2209,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C76" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="3:10" x14ac:dyDescent="0.3">
@@ -2164,39 +2234,39 @@
         <v>0</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C79" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="80" spans="3:10" x14ac:dyDescent="0.3">
@@ -2224,19 +2294,19 @@
         <v>6</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="83" spans="3:10" x14ac:dyDescent="0.3">
@@ -2244,27 +2314,27 @@
         <v>0</v>
       </c>
       <c r="D83" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="84" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C84" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="85" spans="3:10" x14ac:dyDescent="0.3">
@@ -2286,42 +2356,66 @@
         <v>6</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="87" spans="3:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F87" s="13" t="s">
-        <v>106</v>
+      <c r="F87" s="14" t="s">
+        <v>102</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="88" spans="3:10" ht="24" x14ac:dyDescent="0.3">
-      <c r="F88" s="13"/>
+      <c r="C88" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F88" s="15"/>
       <c r="G88" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="89" spans="3:10" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F89" s="13"/>
+      <c r="C89" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F89" s="15"/>
       <c r="G89" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90" spans="3:10" ht="24" x14ac:dyDescent="0.3">
-      <c r="F90" s="13"/>
+      <c r="C90" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F90" s="16"/>
       <c r="G90" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="91" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C91" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>154</v>
+      </c>
       <c r="F91" s="11"/>
       <c r="G91"/>
     </row>
@@ -2330,22 +2424,40 @@
       <c r="G92"/>
     </row>
     <row r="93" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C93" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>157</v>
+      </c>
       <c r="F93" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="94" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C94" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>155</v>
+      </c>
       <c r="F94" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="95" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C95" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="F95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2354,36 +2466,60 @@
       </c>
     </row>
     <row r="96" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C96" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="F96" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="97" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C97"/>
       <c r="D97"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
     </row>
     <row r="98" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C98"/>
-      <c r="D98"/>
+      <c r="C98" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>158</v>
+      </c>
       <c r="F98" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="99" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C99" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>155</v>
+      </c>
       <c r="F99" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="100" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C100" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="F100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2392,11 +2528,17 @@
       </c>
     </row>
     <row r="101" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C101" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>159</v>
+      </c>
       <c r="F101" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="103" spans="3:7" x14ac:dyDescent="0.3">
@@ -2404,15 +2546,15 @@
         <v>0</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="104" spans="3:7" x14ac:dyDescent="0.3">
       <c r="F104" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="105" spans="3:7" x14ac:dyDescent="0.3">
@@ -2428,7 +2570,7 @@
         <v>6</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/Abilities.xlsx
+++ b/Abilities.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="184">
   <si>
     <t>Name</t>
   </si>
@@ -93,9 +93,6 @@
     <t>Covers the cell under unit in "Oil"</t>
   </si>
   <si>
-    <t>First instance of incoming damage deals 0 damage</t>
-  </si>
-  <si>
     <t>Dripping</t>
   </si>
   <si>
@@ -126,9 +123,6 @@
     <t>Infiltrating</t>
   </si>
   <si>
-    <t>Resistant: (Fire/Lightning/Physical)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> -1 (&lt;Damage type&gt;) damage received</t>
   </si>
   <si>
@@ -153,9 +147,6 @@
     <t>Battle-hungry</t>
   </si>
   <si>
-    <t>If hasn't attacked anyone for 2 turns, gains Mad</t>
-  </si>
-  <si>
     <t>Can be deployed in a line right behind enemy's deployment zone, takes 1 extra turn to arrive this way</t>
   </si>
   <si>
@@ -201,24 +192,15 @@
     <t>Applies "Weak" to ALL units within 1 cell</t>
   </si>
   <si>
-    <t>When deployed, places 1 "Stout" and 2 "Sparrow" units</t>
-  </si>
-  <si>
     <t>Bloodthirsty</t>
   </si>
   <si>
-    <t>Can also attack friendly units</t>
-  </si>
-  <si>
     <t>Vampiric</t>
   </si>
   <si>
     <t>Decaying</t>
   </si>
   <si>
-    <t>After beign moved, takes 1 (Physical) damage</t>
-  </si>
-  <si>
     <t>A game of skeletons</t>
   </si>
   <si>
@@ -237,9 +219,6 @@
     <t>At the start of each turn, has 50% chance to gain either "Beckoned" or "Cowardly"</t>
   </si>
   <si>
-    <t>Vulnerable:(Fire/Lightning/Physical)</t>
-  </si>
-  <si>
     <t>Delayed</t>
   </si>
   <si>
@@ -249,9 +228,6 @@
     <t>Woundable</t>
   </si>
   <si>
-    <t>If current half is half the maximu or lower, unit gains Weak</t>
-  </si>
-  <si>
     <t>Unscoring</t>
   </si>
   <si>
@@ -444,9 +420,6 @@
     <t>Name: Base names alphabetically arranged, then abilities additions</t>
   </si>
   <si>
-    <t>At the start of the round, creates a 'Skelic' unit nearby. Afterwards, if if this unit is standing next to 2 or more units with this Ability, it is immedeatly destroyed</t>
-  </si>
-  <si>
     <t>At the start of the round, Merges with all units within 1 cell with this ability</t>
   </si>
   <si>
@@ -483,12 +456,6 @@
     <t>Deals 1 (Physical) damage to all enemies within a 2 cell square ring</t>
   </si>
   <si>
-    <t>""</t>
-  </si>
-  <si>
-    <t>Functions as temporary additional maximum health, but is only restored when additional "Extra health (X)" ability is applied</t>
-  </si>
-  <si>
     <t>Extra healthy (X)</t>
   </si>
   <si>
@@ -499,6 +466,108 @@
   </si>
   <si>
     <t>The first time player uses an item when this unit is on the battlefield, another item is immedeatly drawn</t>
+  </si>
+  <si>
+    <t>After being moved, takes 1 (Physical) damage</t>
+  </si>
+  <si>
+    <t>If hasn't attacked anyone for 2 turns, gains Beckoned</t>
+  </si>
+  <si>
+    <t>Vulnerable:(&lt;Damage type&gt;)</t>
+  </si>
+  <si>
+    <t>Resistant: (&lt;Damage type&gt;)</t>
+  </si>
+  <si>
+    <t>explosive ""</t>
+  </si>
+  <si>
+    <t>sneaky ""</t>
+  </si>
+  <si>
+    <t>When deployed, places 1 "Stout" and 2 "Sparrow" units what gain other abilities of the unit</t>
+  </si>
+  <si>
+    <t>adaptive ""</t>
+  </si>
+  <si>
+    <t>Adaptive (&lt;Damage type&gt;)</t>
+  </si>
+  <si>
+    <t>After taking damage, gains resistance to the type of damage dealt</t>
+  </si>
+  <si>
+    <t>Slowed</t>
+  </si>
+  <si>
+    <t>After moving, must remain stationary next turn</t>
+  </si>
+  <si>
+    <t>Paranoid</t>
+  </si>
+  <si>
+    <t>If deployed closer than 3 cells away from any other units, until the end of the battle, maximum health is decreased by 3 (To a minimum of 1)</t>
+  </si>
+  <si>
+    <t>Terrified</t>
+  </si>
+  <si>
+    <t>At the end of the turn, if no other friendly units are within 3 cells of this unit, this unit takes 1 (Mental) damage</t>
+  </si>
+  <si>
+    <t>Damage types:</t>
+  </si>
+  <si>
+    <t>Physical</t>
+  </si>
+  <si>
+    <t>Lightning</t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>Frost</t>
+  </si>
+  <si>
+    <t>Poison</t>
+  </si>
+  <si>
+    <t>Mental</t>
+  </si>
+  <si>
+    <t>Costly</t>
+  </si>
+  <si>
+    <t>While this unit is a part of your army, you lose 1$ at the end of each shop</t>
+  </si>
+  <si>
+    <t>If current half is half the maximum or lower, unit gains Weak</t>
+  </si>
+  <si>
+    <t>battle hungry ()</t>
+  </si>
+  <si>
+    <t>Attacks also target and damage friendly units</t>
+  </si>
+  <si>
+    <t>"" watched at by Gods</t>
+  </si>
+  <si>
+    <t>Watched by Gods</t>
+  </si>
+  <si>
+    <t>Each time a unit within 1 cells is destroyed, until the end of the Battle, this unit gains a random Ability</t>
+  </si>
+  <si>
+    <t>Has (X) amount of additional maximum health which cannot be healed</t>
+  </si>
+  <si>
+    <t>At the start of the round, creates a 'Skelic' unit nearby. Afterwards, if this unit is standing next to 2 or more units, it is immedeatly destroyed</t>
+  </si>
+  <si>
+    <t>Next instance of incoming damage deals 0 damage. Functions once per battle</t>
   </si>
 </sst>
 </file>
@@ -579,7 +648,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -639,6 +708,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -647,7 +731,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -681,6 +765,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1000,7 +1090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" style="3" customWidth="1"/>
@@ -1017,18 +1107,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
@@ -1038,7 +1128,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1046,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>153</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>0</v>
@@ -1058,28 +1148,28 @@
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>73</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -1107,13 +1197,13 @@
     </row>
     <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>6</v>
@@ -1125,7 +1215,7 @@
         <v>6</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1133,12 +1223,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C9" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>0</v>
@@ -1153,27 +1243,33 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="10" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="14" t="s">
+        <v>166</v>
+      </c>
       <c r="C10" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>167</v>
+      </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
       </c>
@@ -1194,11 +1290,14 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>168</v>
+      </c>
       <c r="C12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>6</v>
@@ -1213,7 +1312,15 @@
         <v>18</v>
       </c>
     </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="C14" s="2" t="s">
         <v>0</v>
       </c>
@@ -1224,36 +1331,42 @@
         <v>0</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>171</v>
+      </c>
       <c r="C15" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="C16" s="2" t="s">
         <v>5</v>
       </c>
@@ -1284,13 +1397,13 @@
         <v>6</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.3">
@@ -1304,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>0</v>
@@ -1335,22 +1448,22 @@
     </row>
     <row r="21" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="22" spans="3:10" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1364,7 +1477,7 @@
         <v>6</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>6</v>
@@ -1378,39 +1491,39 @@
         <v>0</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C25" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="3:10" x14ac:dyDescent="0.3">
@@ -1438,19 +1551,19 @@
         <v>6</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="3:10" x14ac:dyDescent="0.3">
@@ -1464,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>0</v>
@@ -1475,22 +1588,22 @@
     </row>
     <row r="30" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C30" s="7" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="3:10" x14ac:dyDescent="0.3">
@@ -1513,24 +1626,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="3:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>25</v>
+        <v>183</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>6</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.3">
@@ -1538,39 +1651,39 @@
         <v>0</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>0</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C35" s="7" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="3:10" x14ac:dyDescent="0.3">
@@ -1598,19 +1711,19 @@
         <v>6</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>6</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.3">
@@ -1618,965 +1731,1137 @@
         <v>0</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G39" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="3:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="41" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="3:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="44" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C44" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C45" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C46" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C49" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C50" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C51" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="F53" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C54" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C55" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C56" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="59" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C59" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="60" spans="3:10" s="10" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C60" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="61" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C61" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="3:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C64" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="65" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C65" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="66" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C66" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C69" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C70" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="71" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C71" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="3:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="74" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C74" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J74" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I39" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="40" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="4" t="s">
+    </row>
+    <row r="75" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C75" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="76" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C76" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F40" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G40" s="8" t="s">
+      <c r="F76" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G76" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I40" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J40" s="4" t="s">
+      <c r="I76" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J76" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="3:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="43" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C43" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="44" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="45" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C45" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C46" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="48" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C48" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="49" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="50" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C50" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C51" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G51" s="4" t="s">
+    <row r="77" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="79" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C79" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="I51" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="52" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="F52" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="53" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C53" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I53" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="54" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="55" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C55" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C56" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="I56" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="58" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C58" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I58" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="59" spans="3:10" s="10" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C59" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="60" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C60" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I60" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="3:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="C61" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="63" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C63" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I63" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="64" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="I64" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="65" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C65" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I65" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="66" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C66" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J66" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="68" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C68" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="I68" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J68" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="69" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="70" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C70" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J70" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="71" spans="3:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C71" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J71" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="73" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C73" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="I73" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J73" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="74" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C74" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="J74" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="75" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C75" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I75" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J75" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="76" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C76" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="I76" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J76" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="78" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C78" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="79" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C79" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>104</v>
-      </c>
       <c r="F79" s="4" t="s">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="80" spans="3:10" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="80" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C80" s="4" t="s">
-        <v>5</v>
+        <v>112</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>5</v>
+        <v>112</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
     </row>
     <row r="81" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C81" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="83" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C83" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="84" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="84" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C84" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="85" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C85" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="86" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C86" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I86" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C87" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="88" spans="3:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F88" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="89" spans="3:10" ht="24" x14ac:dyDescent="0.3">
+      <c r="C89" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F89" s="17"/>
+      <c r="G89" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="D84" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="85" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C85" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D85" s="4" t="s">
+    </row>
+    <row r="90" spans="3:10" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C90" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F90" s="17"/>
+      <c r="G90" s="9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="91" spans="3:10" ht="24" x14ac:dyDescent="0.3">
+      <c r="C91" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F85" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C86" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="87" spans="3:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F87" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="88" spans="3:10" ht="24" x14ac:dyDescent="0.3">
-      <c r="C88" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="F88" s="15"/>
-      <c r="G88" s="9" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="89" spans="3:10" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C89" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F89" s="15"/>
-      <c r="G89" s="9" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="90" spans="3:10" ht="24" x14ac:dyDescent="0.3">
-      <c r="C90" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F90" s="16"/>
-      <c r="G90" s="9" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="91" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C91" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F91" s="11"/>
-      <c r="G91"/>
+      <c r="F91" s="18"/>
+      <c r="G91" s="9" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="92" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C92" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>145</v>
+      </c>
       <c r="F92" s="11"/>
       <c r="G92"/>
     </row>
     <row r="93" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C93" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>129</v>
-      </c>
+      <c r="F93" s="11"/>
+      <c r="G93"/>
     </row>
     <row r="94" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C94" s="4" t="s">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="95" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C95" s="4" t="s">
-        <v>5</v>
+        <v>112</v>
       </c>
       <c r="D95" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I95" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="96" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C96" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D96" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F95" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G95" s="4" t="s">
+      <c r="F96" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="96" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C96" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G96" s="4" t="s">
+      <c r="I96" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C97" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="98" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C98"/>
+      <c r="D98"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
+    </row>
+    <row r="99" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C99" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="100" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C100" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I100" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="101" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C101" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="3:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C102" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I102" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J102" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="104" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C104" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I104" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J104" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="105" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C105" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G105" s="4" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="97" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C97"/>
-      <c r="D97"/>
-      <c r="F97" s="12"/>
-      <c r="G97" s="12"/>
-    </row>
-    <row r="98" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C98" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G98" s="4" t="s">
+      <c r="I105" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J105" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="106" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C106" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J106" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C107" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G107" s="4" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="99" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C99" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="100" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C100" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="4" t="s">
+      <c r="I107" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J107" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="109" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="F109" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="110" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="F110" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="111" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="F111" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G111" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C101" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="F101" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G101" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="103" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="F103" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G103" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="104" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="F104" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="105" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="F105" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G105" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="F106" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>139</v>
+    <row r="112" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F112" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="F87:F90"/>
+    <mergeCell ref="F88:F91"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Abilities.xlsx
+++ b/Abilities.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="188">
   <si>
     <t>Name</t>
   </si>
@@ -90,9 +90,6 @@
     <t>Oozing</t>
   </si>
   <si>
-    <t>Covers the cell under unit in "Oil"</t>
-  </si>
-  <si>
     <t>Dripping</t>
   </si>
   <si>
@@ -129,9 +126,6 @@
     <t xml:space="preserve"> +1 (&lt;Damage type&gt;) damage received</t>
   </si>
   <si>
-    <t>Covers the cell under unit in "Toxin"</t>
-  </si>
-  <si>
     <t>Conductive</t>
   </si>
   <si>
@@ -568,6 +562,24 @@
   </si>
   <si>
     <t>Next instance of incoming damage deals 0 damage. Functions once per battle</t>
+  </si>
+  <si>
+    <t>"" beckoned by (X)</t>
+  </si>
+  <si>
+    <t>Very slippery</t>
+  </si>
+  <si>
+    <t>very slippery ""</t>
+  </si>
+  <si>
+    <t>After being moved, slips 2 cells in a random direction</t>
+  </si>
+  <si>
+    <t>Covers the cells under itself and units it attacks in "Toxin"</t>
+  </si>
+  <si>
+    <t>Covers the cells under itself and units it attacks in "Oil"</t>
   </si>
 </sst>
 </file>
@@ -1090,23 +1102,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J112"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J117"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="3"/>
-    <col min="3" max="3" width="16.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="72.88671875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="3.88671875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="3"/>
+    <col min="3" max="3" width="16.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="72.85546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="3.85546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" style="3" customWidth="1"/>
     <col min="7" max="7" width="45" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="44.88671875" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="3"/>
+    <col min="8" max="8" width="12.42578125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="44.85546875" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>4</v>
       </c>
@@ -1120,7 +1132,7 @@
       <c r="I1" s="15"/>
       <c r="J1" s="15"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1128,7 +1140,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1136,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>0</v>
@@ -1148,31 +1160,31 @@
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="C5" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
@@ -1197,13 +1209,13 @@
     </row>
     <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>6</v>
@@ -1215,20 +1227,20 @@
         <v>6</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C9" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>0</v>
@@ -1243,32 +1255,32 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="10" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" s="10" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>98</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -1289,21 +1301,21 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>24</v>
+        <v>187</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>6</v>
@@ -1312,14 +1324,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>0</v>
@@ -1331,41 +1343,41 @@
         <v>0</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>5</v>
@@ -1386,7 +1398,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:10" ht="28.9" x14ac:dyDescent="0.3">
       <c r="C17" s="2" t="s">
         <v>6</v>
       </c>
@@ -1397,16 +1409,16 @@
         <v>6</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C19" s="2" t="s">
         <v>0</v>
       </c>
@@ -1417,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>0</v>
@@ -1426,7 +1438,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C20" s="2" t="s">
         <v>5</v>
       </c>
@@ -1446,27 +1458,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C21" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="3:10" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="2" t="s">
         <v>6</v>
       </c>
@@ -1477,7 +1489,7 @@
         <v>6</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>37</v>
+        <v>186</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>6</v>
@@ -1486,47 +1498,47 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C24" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C25" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C26" s="2" t="s">
         <v>5</v>
       </c>
@@ -1546,27 +1558,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:10" ht="45" x14ac:dyDescent="0.25">
       <c r="C27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C29" s="7" t="s">
         <v>0</v>
       </c>
@@ -1577,36 +1589,36 @@
         <v>0</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="J29" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C30" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C31" s="7" t="s">
         <v>5</v>
       </c>
@@ -1619,74 +1631,74 @@
       <c r="G31" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I31" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J31" s="7" t="s">
+      <c r="I31" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J31" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="3:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="3:10" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C34" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>0</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C35" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C36" s="7" t="s">
         <v>5</v>
       </c>
@@ -1706,67 +1718,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C37" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>6</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="39" spans="3:10" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="40" spans="3:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="3:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="41" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="4" t="s">
         <v>5</v>
       </c>
@@ -1786,67 +1798,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="3:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:10" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="44" spans="3:10" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="44" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C44" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C45" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="46" spans="3:10" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="46" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1866,67 +1878,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C47" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J47" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C49" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C49" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C50" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="51" spans="3:10" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C51" s="4" t="s">
         <v>5</v>
       </c>
@@ -1946,75 +1958,75 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C52" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G52" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="F53" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G53" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I52" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="53" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="F53" s="9" t="s">
+    </row>
+    <row r="54" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C54" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F54" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="G54" s="9" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C54" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F54" s="9" t="s">
+      <c r="I54" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F55" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G54" s="9" t="s">
+      <c r="G55" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="I54" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="I55" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C56" s="4" t="s">
         <v>5</v>
       </c>
@@ -2028,61 +2040,61 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C57" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="59" spans="3:10" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="59" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C59" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="60" spans="3:10" s="10" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="3:10" s="10" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="61" spans="3:10" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="61" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C61" s="4" t="s">
         <v>5</v>
       </c>
@@ -2102,67 +2114,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="3:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:10" ht="60" x14ac:dyDescent="0.25">
       <c r="C62" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D62" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C64" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F62" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="I62" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C64" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>59</v>
-      </c>
       <c r="F64" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="65" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C65" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D65" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="F65" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="66" spans="3:10" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="66" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C66" s="4" t="s">
         <v>5</v>
       </c>
@@ -2182,67 +2194,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:10" ht="45" x14ac:dyDescent="0.25">
       <c r="C67" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="69" spans="3:10" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C69" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="70" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C70" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="71" spans="3:10" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="71" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2262,67 +2274,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="3:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:10" ht="55.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="74" spans="3:10" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="74" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C74" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="75" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="75" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C75" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="76" spans="3:10" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="76" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2342,67 +2354,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C77" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G77" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="79" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C79" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I77" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J77" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="79" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C79" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="I79" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="80" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="80" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C80" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="81" spans="3:10" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="81" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2422,67 +2434,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C82" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G82" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="84" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C84" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="I82" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J82" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="84" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C84" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G84" s="4" t="s">
+      <c r="I84" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="85" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C85" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="I84" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J84" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="85" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C85" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="I85" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="86" spans="3:10" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="86" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C86" s="4" t="s">
         <v>5</v>
       </c>
@@ -2502,59 +2514,59 @@
         <v>17</v>
       </c>
     </row>
-    <row r="87" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C87" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="88" spans="3:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="88" spans="3:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F88" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="89" spans="3:10" ht="24" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="89" spans="3:10" ht="24" x14ac:dyDescent="0.25">
       <c r="C89" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F89" s="17"/>
       <c r="G89" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="90" spans="3:10" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="90" spans="3:10" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F90" s="17"/>
       <c r="G90" s="9" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="91" spans="3:10" ht="24" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="91" spans="3:10" ht="24" x14ac:dyDescent="0.25">
       <c r="C91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2563,64 +2575,64 @@
       </c>
       <c r="F91" s="18"/>
       <c r="G91" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="92" spans="3:10" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="92" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C92" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F92" s="11"/>
       <c r="G92"/>
     </row>
-    <row r="93" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F93" s="11"/>
       <c r="G93"/>
     </row>
-    <row r="94" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C94" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="95" spans="3:10" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="95" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C95" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="96" spans="3:10" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2640,73 +2652,73 @@
         <v>17</v>
       </c>
     </row>
-    <row r="97" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:10" ht="60" x14ac:dyDescent="0.25">
       <c r="C97" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="98" spans="3:10" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="98" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C98"/>
       <c r="D98"/>
       <c r="F98" s="12"/>
       <c r="G98" s="12"/>
     </row>
-    <row r="99" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C99" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="100" spans="3:10" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="100" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C100" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="101" spans="3:10" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="101" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2726,67 +2738,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="3:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C102" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="104" spans="3:10" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="104" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C104" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="105" spans="3:10" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="105" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C105" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="106" spans="3:10" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="106" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2806,43 +2818,43 @@
         <v>17</v>
       </c>
     </row>
-    <row r="107" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C107" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="109" spans="3:10" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="109" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F109" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="110" spans="3:10" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="110" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F110" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="111" spans="3:10" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="111" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2850,12 +2862,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:10" ht="45" x14ac:dyDescent="0.25">
       <c r="F112" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="114" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F114" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="115" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F115" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="116" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F116" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="6:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="F117" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2871,9 +2915,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2883,7 +2927,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Abilities.xlsx
+++ b/Abilities.xlsx
@@ -93,9 +93,6 @@
     <t>Dripping</t>
   </si>
   <si>
-    <t>Covers the cell under unit in "Water"</t>
-  </si>
-  <si>
     <t>Penetrating</t>
   </si>
   <si>
@@ -580,6 +577,9 @@
   </si>
   <si>
     <t>Covers the cells under itself and units it attacks in "Oil"</t>
+  </si>
+  <si>
+    <t>Covers the cell under itself and units it attacks in "Water"</t>
   </si>
 </sst>
 </file>
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>0</v>
@@ -1160,28 +1160,28 @@
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="C5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="I5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
@@ -1209,13 +1209,13 @@
     </row>
     <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>6</v>
@@ -1227,7 +1227,7 @@
         <v>6</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1240,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>0</v>
@@ -1257,30 +1257,30 @@
     </row>
     <row r="10" spans="1:10" s="10" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="F10" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G10" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -1303,19 +1303,19 @@
     </row>
     <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>6</v>
@@ -1326,12 +1326,12 @@
     </row>
     <row r="13" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>0</v>
@@ -1349,35 +1349,35 @@
         <v>0</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="F15" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>5</v>
@@ -1398,7 +1398,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="3:10" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C17" s="2" t="s">
         <v>6</v>
       </c>
@@ -1409,13 +1409,13 @@
         <v>6</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>25</v>
+        <v>187</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
@@ -1429,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>0</v>
@@ -1460,22 +1460,22 @@
     </row>
     <row r="21" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C21" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="I21" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="22" spans="3:10" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1489,7 +1489,7 @@
         <v>6</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>6</v>
@@ -1503,39 +1503,39 @@
         <v>0</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C25" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J25" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="26" spans="3:10" x14ac:dyDescent="0.25">
@@ -1563,19 +1563,19 @@
         <v>6</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="3:10" x14ac:dyDescent="0.25">
@@ -1589,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>0</v>
@@ -1600,22 +1600,22 @@
     </row>
     <row r="30" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C30" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>94</v>
-      </c>
       <c r="F30" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G30" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>103</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="31" spans="3:10" x14ac:dyDescent="0.25">
@@ -1643,19 +1643,19 @@
         <v>6</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I32" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.25">
@@ -1663,39 +1663,39 @@
         <v>0</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>0</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C35" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>94</v>
-      </c>
       <c r="F35" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G35" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="G35" s="8" t="s">
-        <v>94</v>
-      </c>
       <c r="I35" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="J35" s="7" t="s">
         <v>93</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="36" spans="3:10" x14ac:dyDescent="0.25">
@@ -1723,19 +1723,19 @@
         <v>6</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>6</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.25">
@@ -1743,39 +1743,39 @@
         <v>0</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="3:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1803,19 +1803,19 @@
         <v>6</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" spans="3:10" x14ac:dyDescent="0.25">
@@ -1823,39 +1823,39 @@
         <v>0</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C45" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D45" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="F45" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G45" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J45" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="46" spans="3:10" x14ac:dyDescent="0.25">
@@ -1883,19 +1883,19 @@
         <v>6</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="3:10" x14ac:dyDescent="0.25">
@@ -1903,39 +1903,39 @@
         <v>0</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C50" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G50" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="I50" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J50" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="51" spans="3:10" x14ac:dyDescent="0.25">
@@ -1963,27 +1963,27 @@
         <v>6</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F53" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G53" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="54" spans="3:10" x14ac:dyDescent="0.25">
@@ -1991,39 +1991,39 @@
         <v>0</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F54" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G54" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="G54" s="9" t="s">
-        <v>76</v>
-      </c>
       <c r="I54" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C55" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="F55" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G55" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G55" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="I55" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="3:10" x14ac:dyDescent="0.25">
@@ -2045,13 +2045,13 @@
         <v>6</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="59" spans="3:10" x14ac:dyDescent="0.25">
@@ -2059,39 +2059,39 @@
         <v>0</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="3:10" s="10" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G60" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="I60" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="3:10" x14ac:dyDescent="0.25">
@@ -2119,19 +2119,19 @@
         <v>6</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="3:10" x14ac:dyDescent="0.25">
@@ -2139,39 +2139,39 @@
         <v>0</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C65" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D65" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G65" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="F65" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="I65" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="3:10" x14ac:dyDescent="0.25">
@@ -2199,19 +2199,19 @@
         <v>6</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="3:10" x14ac:dyDescent="0.25">
@@ -2219,39 +2219,39 @@
         <v>0</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C70" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="71" spans="3:10" x14ac:dyDescent="0.25">
@@ -2279,19 +2279,19 @@
         <v>6</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74" spans="3:10" x14ac:dyDescent="0.25">
@@ -2299,39 +2299,39 @@
         <v>0</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C75" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="76" spans="3:10" x14ac:dyDescent="0.25">
@@ -2359,19 +2359,19 @@
         <v>6</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="3:10" x14ac:dyDescent="0.25">
@@ -2379,39 +2379,39 @@
         <v>0</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="80" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C80" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I80" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J80" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="J80" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="81" spans="3:10" x14ac:dyDescent="0.25">
@@ -2439,19 +2439,19 @@
         <v>6</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="84" spans="3:10" x14ac:dyDescent="0.25">
@@ -2459,39 +2459,39 @@
         <v>0</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="85" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C85" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I85" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J85" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="J85" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="86" spans="3:10" x14ac:dyDescent="0.25">
@@ -2519,27 +2519,27 @@
         <v>6</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="88" spans="3:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F88" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="89" spans="3:10" ht="24" x14ac:dyDescent="0.25">
@@ -2547,23 +2547,23 @@
         <v>0</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F89" s="17"/>
       <c r="G89" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="90" spans="3:10" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F90" s="17"/>
       <c r="G90" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="91" spans="3:10" ht="24" x14ac:dyDescent="0.25">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="F91" s="18"/>
       <c r="G91" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="3:10" x14ac:dyDescent="0.25">
@@ -2583,7 +2583,7 @@
         <v>6</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F92" s="11"/>
       <c r="G92"/>
@@ -2597,39 +2597,39 @@
         <v>0</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="95" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C95" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I95" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J95" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="J95" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="96" spans="3:10" x14ac:dyDescent="0.25">
@@ -2657,19 +2657,19 @@
         <v>6</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="98" spans="3:10" x14ac:dyDescent="0.25">
@@ -2683,39 +2683,39 @@
         <v>0</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="100" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C100" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I100" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J100" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="J100" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="101" spans="3:10" x14ac:dyDescent="0.25">
@@ -2743,19 +2743,19 @@
         <v>6</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="104" spans="3:10" x14ac:dyDescent="0.25">
@@ -2763,39 +2763,39 @@
         <v>0</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="105" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C105" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I105" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J105" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="J105" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="106" spans="3:10" x14ac:dyDescent="0.25">
@@ -2823,19 +2823,19 @@
         <v>6</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="109" spans="3:10" x14ac:dyDescent="0.25">
@@ -2843,15 +2843,15 @@
         <v>0</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="110" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F110" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="111" spans="3:10" x14ac:dyDescent="0.25">
@@ -2867,7 +2867,7 @@
         <v>6</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="114" spans="6:7" x14ac:dyDescent="0.25">
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="115" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F115" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="116" spans="6:7" x14ac:dyDescent="0.25">
@@ -2899,7 +2899,7 @@
         <v>6</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/Abilities.xlsx
+++ b/Abilities.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1103,22 +1103,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J117"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" style="3"/>
-    <col min="3" max="3" width="16.28515625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="72.85546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="3.85546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="3"/>
+    <col min="3" max="3" width="16.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="72.88671875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="3.88671875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="3" customWidth="1"/>
     <col min="7" max="7" width="45" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="44.85546875" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="3"/>
+    <col min="8" max="8" width="12.44140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="44.88671875" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>4</v>
       </c>
@@ -1132,7 +1132,7 @@
       <c r="I1" s="15"/>
       <c r="J1" s="15"/>
     </row>
-    <row r="2" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1140,7 +1140,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="4" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="C5" s="1" t="s">
         <v>92</v>
@@ -1184,7 +1184,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
@@ -1230,12 +1230,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:10" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="10" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" s="10" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
         <v>163</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>164</v>
       </c>
@@ -1324,12 +1324,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>167</v>
       </c>
@@ -1339,10 +1339,10 @@
       <c r="D14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7" t="s">
+      <c r="F14" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>24</v>
       </c>
       <c r="I14" s="4" t="s">
@@ -1352,7 +1352,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>168</v>
       </c>
@@ -1362,10 +1362,10 @@
       <c r="D15" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G15" s="7" t="s">
+      <c r="F15" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="8" t="s">
         <v>97</v>
       </c>
       <c r="I15" s="4" t="s">
@@ -1375,7 +1375,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>169</v>
       </c>
@@ -1385,10 +1385,10 @@
       <c r="D16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G16" s="7" t="s">
+      <c r="F16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>8</v>
       </c>
       <c r="I16" s="4" t="s">
@@ -1398,17 +1398,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G17" s="7" t="s">
+      <c r="F17" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="8" t="s">
         <v>187</v>
       </c>
       <c r="I17" s="4" t="s">
@@ -1418,17 +1418,17 @@
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C19" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="F19" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8" t="s">
         <v>49</v>
       </c>
       <c r="I19" s="2" t="s">
@@ -1438,17 +1438,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C20" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="F20" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="8" t="s">
         <v>8</v>
       </c>
       <c r="I20" s="2" t="s">
@@ -1458,17 +1458,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C21" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="F21" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>99</v>
       </c>
       <c r="I21" s="2" t="s">
@@ -1478,17 +1478,17 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="3:10" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:10" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="F22" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>185</v>
       </c>
       <c r="I22" s="2" t="s">
@@ -1498,91 +1498,91 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C24" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="F24" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="s">
+      <c r="I24" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C25" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="F25" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I25" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="J25" s="4" t="s">
+      <c r="I25" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C26" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G26" s="4" t="s">
+      <c r="F26" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I26" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J26" s="4" t="s">
+      <c r="I26" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="3:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G27" s="4" t="s">
+      <c r="F27" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="I27" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J27" s="4" t="s">
+      <c r="I27" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C29" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D29" s="7" t="s">
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F29" s="4" t="s">
@@ -1598,11 +1598,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" s="7" t="s">
+    <row r="30" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C30" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>93</v>
       </c>
       <c r="F30" s="4" t="s">
@@ -1618,11 +1618,11 @@
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C31" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="7" t="s">
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F31" s="4" t="s">
@@ -1638,11 +1638,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="3:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="7" t="s">
+    <row r="32" spans="3:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>180</v>
       </c>
       <c r="F32" s="4" t="s">
@@ -1658,11 +1658,11 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C34" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D34" s="7" t="s">
+    <row r="34" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C34" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>27</v>
       </c>
       <c r="F34" s="8" t="s">
@@ -1671,18 +1671,18 @@
       <c r="G34" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="I34" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="J34" s="7" t="s">
+      <c r="I34" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J34" s="8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D35" s="7" t="s">
+    <row r="35" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>93</v>
       </c>
       <c r="F35" s="8" t="s">
@@ -1691,18 +1691,18 @@
       <c r="G35" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="I35" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="J35" s="7" t="s">
+      <c r="I35" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J35" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C36" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="7" t="s">
+    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C36" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F36" s="8" t="s">
@@ -1711,18 +1711,18 @@
       <c r="G36" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I36" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J36" s="7" t="s">
+      <c r="I36" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J36" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="3:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="C37" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="7" t="s">
+    <row r="37" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C37" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="8" t="s">
         <v>36</v>
       </c>
       <c r="F37" s="8" t="s">
@@ -1731,18 +1731,18 @@
       <c r="G37" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I37" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="J37" s="7" t="s">
+      <c r="I37" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J37" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C39" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D39" s="4" t="s">
+    <row r="39" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C39" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F39" s="8" t="s">
@@ -1758,11 +1758,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="3:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D40" s="4" t="s">
+    <row r="40" spans="3:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D40" s="8" t="s">
         <v>152</v>
       </c>
       <c r="F40" s="8" t="s">
@@ -1778,11 +1778,11 @@
         <v>173</v>
       </c>
     </row>
-    <row r="41" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" s="4" t="s">
+    <row r="41" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F41" s="8" t="s">
@@ -1798,11 +1798,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="3:10" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="4" t="s">
+    <row r="42" spans="3:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="8" t="s">
         <v>40</v>
       </c>
       <c r="F42" s="8" t="s">
@@ -1818,7 +1818,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="44" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C44" s="4" t="s">
         <v>0</v>
       </c>
@@ -1831,14 +1831,14 @@
       <c r="G44" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="I44" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J44" s="4" t="s">
+      <c r="I44" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J44" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C45" s="4" t="s">
         <v>92</v>
       </c>
@@ -1851,14 +1851,14 @@
       <c r="G45" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="I45" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="J45" s="4" t="s">
+      <c r="I45" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J45" s="8" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1871,14 +1871,14 @@
       <c r="G46" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I46" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J46" s="4" t="s">
+      <c r="I46" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C47" s="4" t="s">
         <v>6</v>
       </c>
@@ -1891,24 +1891,24 @@
       <c r="G47" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="I47" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J47" s="4" t="s">
+      <c r="I47" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J47" s="8" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="49" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C49" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D49" s="4" t="s">
+    <row r="49" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C49" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D49" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G49" s="4" t="s">
+      <c r="F49" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G49" s="7" t="s">
         <v>70</v>
       </c>
       <c r="I49" s="4" t="s">
@@ -1918,17 +1918,17 @@
         <v>55</v>
       </c>
     </row>
-    <row r="50" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C50" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D50" s="4" t="s">
+    <row r="50" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C50" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D50" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G50" s="4" t="s">
+      <c r="F50" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G50" s="7" t="s">
         <v>93</v>
       </c>
       <c r="I50" s="4" t="s">
@@ -1938,17 +1938,17 @@
         <v>107</v>
       </c>
     </row>
-    <row r="51" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C51" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" s="4" t="s">
+    <row r="51" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C51" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F51" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G51" s="4" t="s">
+      <c r="F51" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G51" s="7" t="s">
         <v>8</v>
       </c>
       <c r="I51" s="4" t="s">
@@ -1958,17 +1958,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="3:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="C52" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D52" s="4" t="s">
+    <row r="52" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C52" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="F52" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G52" s="4" t="s">
+      <c r="F52" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G52" s="7" t="s">
         <v>71</v>
       </c>
       <c r="I52" s="4" t="s">
@@ -1978,25 +1978,25 @@
         <v>174</v>
       </c>
     </row>
-    <row r="53" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="F53" s="9" t="s">
+    <row r="53" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="F53" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="G53" s="7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C54" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="9" t="s">
+      <c r="F54" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="G54" s="9" t="s">
+      <c r="G54" s="7" t="s">
         <v>75</v>
       </c>
       <c r="I54" s="4" t="s">
@@ -2006,17 +2006,17 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C55" s="4" t="s">
         <v>92</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="F55" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G55" s="9" t="s">
+      <c r="G55" s="7" t="s">
         <v>77</v>
       </c>
       <c r="I55" s="4" t="s">
@@ -2026,7 +2026,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C56" s="4" t="s">
         <v>5</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C57" s="4" t="s">
         <v>6</v>
       </c>
@@ -2054,11 +2054,11 @@
         <v>147</v>
       </c>
     </row>
-    <row r="59" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C59" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D59" s="4" t="s">
+    <row r="59" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C59" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D59" s="8" t="s">
         <v>51</v>
       </c>
       <c r="F59" s="4" t="s">
@@ -2074,11 +2074,11 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="3:10" s="10" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C60" s="4" t="s">
+    <row r="60" spans="3:10" s="10" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C60" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="8" t="s">
         <v>93</v>
       </c>
       <c r="F60" s="4" t="s">
@@ -2094,11 +2094,11 @@
         <v>93</v>
       </c>
     </row>
-    <row r="61" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C61" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="4" t="s">
+    <row r="61" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C61" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F61" s="4" t="s">
@@ -2114,11 +2114,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="3:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="C62" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D62" s="4" t="s">
+    <row r="62" spans="3:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C62" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="8" t="s">
         <v>54</v>
       </c>
       <c r="F62" s="4" t="s">
@@ -2134,7 +2134,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C64" s="4" t="s">
         <v>0</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C65" s="4" t="s">
         <v>109</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="66" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C66" s="4" t="s">
         <v>5</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="3:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C67" s="4" t="s">
         <v>6</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C69" s="4" t="s">
         <v>0</v>
       </c>
@@ -2227,14 +2227,14 @@
       <c r="G69" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="I69" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J69" s="4" t="s">
+      <c r="I69" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J69" s="8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C70" s="4" t="s">
         <v>109</v>
       </c>
@@ -2247,14 +2247,14 @@
       <c r="G70" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="I70" s="4" t="s">
+      <c r="I70" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="J70" s="4" t="s">
+      <c r="J70" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="71" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2267,14 +2267,14 @@
       <c r="G71" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I71" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J71" s="4" t="s">
+      <c r="I71" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J71" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="3:10" ht="55.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C72" s="4" t="s">
         <v>6</v>
       </c>
@@ -2287,14 +2287,14 @@
       <c r="G72" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="I72" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J72" s="4" t="s">
+      <c r="I72" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J72" s="8" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="74" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C74" s="4" t="s">
         <v>0</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C75" s="4" t="s">
         <v>109</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="76" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C77" s="4" t="s">
         <v>6</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="79" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C79" s="4" t="s">
         <v>0</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="80" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C80" s="4" t="s">
         <v>109</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="81" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C82" s="4" t="s">
         <v>6</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="84" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C84" s="4" t="s">
         <v>0</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="85" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C85" s="4" t="s">
         <v>109</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="86" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C86" s="4" t="s">
         <v>5</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="87" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C87" s="4" t="s">
         <v>6</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="88" spans="3:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F88" s="16" t="s">
         <v>91</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="89" spans="3:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:10" ht="24" x14ac:dyDescent="0.3">
       <c r="C89" s="4" t="s">
         <v>0</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="90" spans="3:10" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:10" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C90" s="4" t="s">
         <v>109</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="91" spans="3:10" ht="24" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:10" ht="24" x14ac:dyDescent="0.3">
       <c r="C91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="92" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C92" s="4" t="s">
         <v>6</v>
       </c>
@@ -2588,11 +2588,11 @@
       <c r="F92" s="11"/>
       <c r="G92"/>
     </row>
-    <row r="93" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F93" s="11"/>
       <c r="G93"/>
     </row>
-    <row r="94" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C94" s="4" t="s">
         <v>0</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="95" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C95" s="4" t="s">
         <v>109</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="97" spans="3:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C97" s="4" t="s">
         <v>6</v>
       </c>
@@ -2672,13 +2672,13 @@
         <v>160</v>
       </c>
     </row>
-    <row r="98" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C98"/>
       <c r="D98"/>
       <c r="F98" s="12"/>
       <c r="G98" s="12"/>
     </row>
-    <row r="99" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C99" s="4" t="s">
         <v>0</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="100" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C100" s="4" t="s">
         <v>109</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="101" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="3:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C102" s="4" t="s">
         <v>6</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="104" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C104" s="4" t="s">
         <v>0</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="105" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C105" s="4" t="s">
         <v>109</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="106" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="107" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C107" s="4" t="s">
         <v>6</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="109" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F109" s="4" t="s">
         <v>0</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="110" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F110" s="4" t="s">
         <v>109</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="111" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="3:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="F112" s="4" t="s">
         <v>6</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="114" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F114" s="4" t="s">
         <v>0</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="115" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F115" s="4" t="s">
         <v>109</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="116" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="6:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="117" spans="6:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="F117" s="4" t="s">
         <v>6</v>
       </c>
@@ -2915,9 +2915,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2927,7 +2927,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
